--- a/光伏配储项目/电价数据/2026/门前站.xlsx
+++ b/光伏配储项目/电价数据/2026/门前站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.94545</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.24008</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.05438</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5907899999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.88854</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.53266</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44157</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45906</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43144</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42453</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40445</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42016</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42403</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41708</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42722</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50124</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12267</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.13487</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14097</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07381</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11365</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.5395399999999999</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.21195</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.7674500000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.19628</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14781</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21925</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22944</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23469</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21865</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.68153</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.42127</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14885</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.52908</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.68167</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.77278</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.9562</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7310800000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.6605</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43129</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65822</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.18878</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.7966599999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.5252</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.37607</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.6057</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.76461</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.00805</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.06589</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.78545</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.32608</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.87114</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79647</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7570399999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5175599999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47952</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46888</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42537</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70817</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76885</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8712000000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91591</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49425</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5146799999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50256</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5027900000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48506</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46719</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8763</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7196</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.8150599999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45616</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5087</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5057900000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.77695</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99102</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52137</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8447899999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.49631</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7233200000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.31265</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.07551</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.02484</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46969</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5450499999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5222</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.92161</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62233</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.94968</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.32634</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.54816</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17686</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.12201</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.59424</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.49642</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.6518</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.43012</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.48133</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.03808</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.3738</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9020900000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.45689</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.54823</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.36335</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.14738</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78701</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80779</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44898</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3346</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50768</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48672</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48716</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44759</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42762</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44306</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47206</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.50271</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.6848200000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.90158</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.81814</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.25018</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.55386</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.49543</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.81808</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7231799999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8117000000000001</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5279299999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5474199999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7991200000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.23034</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.68176</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.59782</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49347</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.4456</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.78513</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.52079</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50417</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57009</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5953200000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54265</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.56249</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26486</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61629</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.18267</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.50436</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5346599999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57564</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.97433</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.03604</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.40789</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.8586699999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.83509</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.67386</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.9263899999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61022</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.90552</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56259</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.30897</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.87073</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55943</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48196</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61566</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.51446</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34195</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52166</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49371</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44452</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.52518</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.75951</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.63963</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.87737</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.21031</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.80522</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.93498</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.41417</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.70159</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.43099</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.27061</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.18154</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.02267</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.51319</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.97196</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45634</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6043099999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.42267</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47982</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40465</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.95041</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.95414</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.83723</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.39583</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.46728</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49514</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45024</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46172</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47411</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51975</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.03489</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.93396</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.46066</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.00019</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.8893300000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.8121</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.76191</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.65116</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.54898</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.54477</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31754</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7219099999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.8450299999999999</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.44354</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.19841</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.45323</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.42289</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22004</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15563</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.40195</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27063</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18919</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.51409</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.48705</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05053</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22408</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.44673</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21022</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06345000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.10222</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.00087</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00257</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.04214</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4614</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48656</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34439</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.59097</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10275</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01526</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21621</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05425</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20516</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.06617000000000001</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07036000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3316</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31308</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78523</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87767</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.16711</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.84777</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44936</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.55999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41245</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58494</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70917</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8766699999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46656</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55338</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.81957</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.57262</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85326</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6316499999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6342899999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5924299999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.30274</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42456</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3472</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9140499999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44497</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.46369</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18843</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1978</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25379</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.11641</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.53664</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.86751</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44379</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13995</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68712</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7774500000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6387999999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5092099999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44063</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49059</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40569</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.4646</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42637</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38872</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40672</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40523</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4074700000000001</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48701</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5255700000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.23146</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24839</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15514</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27441</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25995</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25306</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.54398</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43445</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.78951</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43574</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44137</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30825</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.24762</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.25186</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27692</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26482</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22918</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.23273</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28356</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.29409</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.23985</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.28803</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24718</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.29302</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.45024</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40318</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42568</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41897</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.42298</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33542</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.49407</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43748</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.40091</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.92511</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.85602</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25184</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27844</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23951</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.52444</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.54435</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.5954700000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.54498</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.42251</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.85075</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.9234199999999999</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.87822</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.11324</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.7712599999999999</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.14873</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.44885</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37265</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.43303</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.43211</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.42658</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.72605</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.48152</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3494</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.46349</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47605</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.70268</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.81436</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.8025800000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.51568</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.73621</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.4665</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.14344</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.8181499999999999</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.80204</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.10947</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.77274</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.30487</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.21058</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.7238</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.13853</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.31829</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.61882</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.48506</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.29141</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.52886</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.68618</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.55009</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.70277</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.3001</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.60431</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.03887</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.7755599999999999</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.36893</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.78335</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.7500399999999999</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.83873</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.76571</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.76091</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.32719</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.8874</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.73339</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.8673500000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.84927</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.12406</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.79645</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.66308</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.61425</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5220900000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5038</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24111</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>1.58308</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31251</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.92788</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.0843</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.49665</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.87483</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.23006</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47091</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.14274</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.5324800000000001</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.8996000000000001</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.89649</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34348</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75078</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.3212</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.42127</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.54943</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.42589</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5913200000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.42213</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.45028</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.6323300000000001</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65101</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.6968</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.6251100000000001</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.90383</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.7206699999999999</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33474</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.46983</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.48184</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.8806499999999999</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.5835399999999999</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.94424</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.47705</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.68751</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.0097</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.71078</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.7619400000000001</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.57808</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.9249400000000001</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.7906599999999999</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.36437</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.73712</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.71508</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.9877</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.74481</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.98011</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.43541</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.40989</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.44071</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.04667</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.00449</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.43072</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.91544</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.10748</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.92775</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.89125</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.80255</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.48378</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.4049</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.77011</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35107</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45658</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5300199999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47642</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.62029</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38174</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.50613</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.46131</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45839</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.59901</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.31477</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.9721599999999999</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.36201</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.39863</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.47832</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.90488</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.90615</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.9276599999999999</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.57828</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.81762</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.8489099999999999</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.84001</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.9193600000000001</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.16849</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.20174</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.53275</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.8929</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.89438</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.8847</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.88385</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.45956</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.47364</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.47388</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5071100000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6254999999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.73436</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.8237100000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.59141</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.71584</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.10273</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.42815</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.73653</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7653</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6180800000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66642</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.62727</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.02214</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44953</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44581</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43896</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50746</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41756</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42822</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42836</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41828</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.43833</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.89995</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.86954</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.86611</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.88627</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.87536</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>1.3803</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.8873300000000001</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.9665199999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.9239400000000001</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.9765900000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15273</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21744</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.89638</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.5463600000000001</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42511</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42577</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.33352</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.46145</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.56061</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.27015</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.26245</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.2615</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.25647</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.25179</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18965</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24498</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27334</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26169</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25797</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.09915</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27582</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25707</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03469</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28157</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19399</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24882</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24022</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27587</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.41128</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43724</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.6674500000000001</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.6699400000000001</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.43026</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.50505</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32485</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.15019</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.27485</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.24395</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.25331</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.24341</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.24607</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.24606</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.24278</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.24278</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.24475</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.24278</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.2431</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.24356</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.24335</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25031</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16683</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26713</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01293</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00023</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01536</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04075</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02924</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27448</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03823</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01886</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03614</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20152</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26487</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28839</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.33205</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.73781</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.63464</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.43089</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42491</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26516</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26336</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24481</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26926</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26576</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43688</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.26963</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.68324</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8410700000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87714</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8509099999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11451</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21724</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25822</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27106</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27368</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05986</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25509</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47124</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.50096</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.79216</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.74693</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7710199999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.34247</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9809099999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.7626000000000001</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.83526</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.79408</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84037</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83856</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84287</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9400599999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.7543300000000001</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.79003</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.75734</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.364</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46717</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.61161</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.6601399999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5733200000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49375</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.46253</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.28554</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.46287</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.47459</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42564</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.45186</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41434</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26664</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.42954</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.71688</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.59151</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.4593</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.47234</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33818</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.40676</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.55386</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.76439</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.5396799999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.55479</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.44706</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.47499</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.60714</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.5734</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.59742</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.6455299999999999</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.48244</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.56184</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.58188</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.78163</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.90689</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47839</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.31951</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.37505</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.04689</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.47967</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.70132</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.71221</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.55889</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.45752</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.4558</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.92543</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1.24225</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.52117</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.64608</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.52318</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.42116</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23523</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35265</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43496</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.45629</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.8567100000000001</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.49956</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.96161</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.60046</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.45898</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.7419600000000001</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.57369</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.3953</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5121599999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.17078</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7077</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.99391</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6389</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47566</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.25453</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.4654</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.35965</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.28369</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.8316</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>1.07553</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.98726</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.48904</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35704</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.23318</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.56568</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.80328</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>1.6246</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.83916</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.6708</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.8076100000000001</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.7771699999999999</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.8986499999999999</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.80359</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.8241900000000001</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.49142</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.58473</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.78871</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.49929</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.52524</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.87088</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.7332799999999999</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.88934</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.9157000000000001</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.76204</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48492</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.94843</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.8969199999999999</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.9352200000000001</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.89977</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.62314</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.5202899999999999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40664</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.67987</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36376</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.40851</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.25061</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5592699999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.7847799999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.61997</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.4067</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.52573</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.06506</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.6058</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.7355</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.0194</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.5662999999999999</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42686</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.54279</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.63102</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.92077</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.7793600000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.7289600000000001</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.54888</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.53959</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.71983</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.7447699999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.9741000000000001</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.30509</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.14389</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.63517</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35897</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41515</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.37149</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1.36556</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.35543</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>1.34952</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17558</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14526</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19792</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14172</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04456</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12129</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22579</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26543</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15086</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14373</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.19573</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>1.30407</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22606</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.26199</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15292</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19665</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14261</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.63962</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.08059</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.52081</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.53837</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>1.68613</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>1.08277</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.7038300000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.5144299999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.77228</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.5646599999999999</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5720499999999999</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.54906</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.67638</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5577799999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5515599999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.61491</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38453</v>
       </c>
     </row>
   </sheetData>
